--- a/WRExcel/RPC_CHAT_EXCEL.xlsx
+++ b/WRExcel/RPC_CHAT_EXCEL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moon\source\repos\WRExcel\WRExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WRExcel\WRExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439F679B-CC91-488F-9E21-A662BF8BC455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A864E-C3FF-416F-8355-E0FBAAB43D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="4320" windowWidth="25230" windowHeight="15220" tabRatio="564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15460" tabRatio="564" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struct" sheetId="1" r:id="rId1"/>
@@ -39,28 +39,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="88">
   <si>
     <t>NULL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>char</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>st_Header</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CTS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -69,11 +57,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>st_Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>str[50]</t>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOGIN_CONNECT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인 실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SECELT_CHANNEL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채널 선택 실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERROR_CODE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -81,301 +85,213 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Vector2F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>NOT_ERROR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAX_CHANNEL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채널 인원 많음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOGIN_ERROR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채널 입장 실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 선택 실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT_CHARID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OBJECT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLAYER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MONSTER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DROPITEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATTACK_FAIL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FIND_PATH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_MOVE_BY_WALL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_FIND_MAP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map 찾을수가 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FAILD_ATTACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 실패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT_MOVE_BY_ATTACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSVC</t>
+  </si>
+  <si>
+    <t>net_uint32</t>
+  </si>
+  <si>
+    <t>net_uint64</t>
+  </si>
+  <si>
+    <t>net_double</t>
+  </si>
+  <si>
+    <t>__int8</t>
+  </si>
+  <si>
+    <t>__int16</t>
+  </si>
+  <si>
+    <t>__int32</t>
+  </si>
+  <si>
+    <t>__int64</t>
+  </si>
+  <si>
+    <t>unsigned __int8</t>
+  </si>
+  <si>
+    <t>unsigned __int16</t>
+  </si>
+  <si>
+    <t>unsigned __int32</t>
+  </si>
+  <si>
+    <t>unsigned __int64</t>
   </si>
   <si>
     <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NULL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOGIN_CONNECT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로그인 실패</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SECELT_CHANNEL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>채널 선택 실패</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERROR_CODE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NULL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NOT_ERROR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAX_CHANNEL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>채널 인원 많음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOGIN_ERROR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>채널 입장 실패</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_Character_Info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>charID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name[25]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_ErrorResult</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ret</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐릭터 선택 실패</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT_CHARID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OBJECT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLAYER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MONSTER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DROPITEM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATTACK_FAIL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>st_TilePos</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NOT_FIND_PATH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NOT_MOVE_BY_WALL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NOT_FIND_MAP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>map 찾을수가 없음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FAILD_ATTACK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 실패</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NOT_MOVE_BY_ATTACK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MSVC</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>net_char</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cshap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Byte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Int16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Int64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>END</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UByte</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UInt16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UInt32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UInt64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_int8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_int16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_int32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_int64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_uint8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>net_uint16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>net_uint32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>net_uint64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>net_double</t>
-  </si>
-  <si>
-    <t>__int8</t>
-  </si>
-  <si>
-    <t>__int16</t>
-  </si>
-  <si>
-    <t>__int32</t>
-  </si>
-  <si>
-    <t>__int64</t>
-  </si>
-  <si>
-    <t>unsigned __int8</t>
-  </si>
-  <si>
-    <t>unsigned __int16</t>
-  </si>
-  <si>
-    <t>unsigned __int32</t>
-  </si>
-  <si>
-    <t>unsigned __int64</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>net_char</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cshap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Byte</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Int16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Int32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Int64</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>END</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UByte</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UInt16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UInt32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UInt64</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aTest[10]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>testvalue[10]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fv</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_int8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_int16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_int32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_int64</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_uint8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_uint16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_uint32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_uint64</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>net_double</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>afv[100]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -785,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -804,7 +720,7 @@
     <col min="15" max="15" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -815,22 +731,22 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="H1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -841,343 +757,163 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" t="s">
         <v>80</v>
       </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="G6" t="s">
         <v>74</v>
       </c>
-      <c r="K2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="H6" t="s">
         <v>76</v>
       </c>
-      <c r="M2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" t="s">
-        <v>95</v>
-      </c>
-      <c r="H13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" t="s">
-        <v>97</v>
+        <v>81</v>
+      </c>
+      <c r="G11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1198,10 +934,10 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>101</v>
@@ -1209,10 +945,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
@@ -1220,10 +956,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
@@ -1248,10 +984,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C1">
         <v>111</v>
@@ -1259,10 +995,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>222</v>
@@ -1270,10 +1006,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>333</v>
@@ -1281,91 +1017,91 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>0</v>
@@ -1373,10 +1109,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>0</v>
@@ -1384,10 +1120,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
         <v>0</v>
@@ -1395,10 +1131,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>0</v>
@@ -1406,30 +1142,30 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1449,225 +1185,225 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" t="s">
         <v>50</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
